--- a/outputs/Block4_Lowest_Sensitivity_v12.xlsx
+++ b/outputs/Block4_Lowest_Sensitivity_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
   <si>
     <t>Variable</t>
   </si>
@@ -109,33 +109,33 @@
     <t>RSenLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DSenLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DHouLeanResH  (&gt;1&lt;=5%)</t>
+    <t>RHouLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RHouSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DHouTiltResLR (&lt;=1%)</t>
   </si>
   <si>
     <t>DSenLeanResH  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DHouSafResLR (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenSafResLD (&gt;10%)</t>
+    <t>DHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
   </si>
   <si>
     <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>DSenTiltResLR (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
     <t>Senate Buckets</t>
   </si>
   <si>
@@ -152,9 +152,6 @@
   </si>
   <si>
     <t>Moderate-low sensitivity</t>
-  </si>
-  <si>
-    <t>Moderate sensitivity</t>
   </si>
 </sst>
 </file>
@@ -648,10 +645,10 @@
         <v>42</v>
       </c>
       <c r="P2">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="Q2">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -660,10 +657,10 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.1597411054555158</v>
+        <v>0.141286249557361</v>
       </c>
       <c r="U2">
-        <v>-0.1597411054555158</v>
+        <v>-0.141286249557361</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
@@ -689,82 +686,82 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
-        <v>0.66</v>
+        <v>15.048</v>
       </c>
       <c r="D3">
-        <v>0.756</v>
+        <v>14.824</v>
       </c>
       <c r="E3">
-        <v>0.8217382316493707</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="F3">
-        <v>0.6</v>
+        <v>14.2</v>
       </c>
       <c r="G3">
-        <v>0.7051224071145452</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>0.8217382316493707</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="L3">
-        <v>1.559831022862906</v>
+        <v>6.129350049043507</v>
       </c>
       <c r="M3">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
       <c r="P3">
-        <v>0.6715511146470821</v>
+        <v>14.85295632081913</v>
       </c>
       <c r="Q3">
-        <v>0.8172324090351291</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>-0.1501871170022886</v>
+        <v>-0.152258195218657</v>
       </c>
       <c r="U3">
-        <v>0.3284488853529179</v>
+        <v>0.1470436791808698</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>0.7051224071145452</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="X3">
-        <v>0.1166158245348254</v>
+        <v>0.06532640615151664</v>
       </c>
       <c r="Y3">
-        <v>0.1782617683506293</v>
+        <v>0.00521451603778722</v>
       </c>
       <c r="Z3">
-        <v>0.0747618317789252</v>
+        <v>0.01065796628171219</v>
       </c>
       <c r="AA3">
-        <v>0.1142827432829542</v>
+        <v>0.0008507453475594778</v>
       </c>
       <c r="AB3">
-        <v>1.299859185719089</v>
+        <v>0.972912706197382</v>
       </c>
       <c r="AC3">
-        <v>91.52169382676631</v>
+        <v>99.2800601772977</v>
       </c>
       <c r="AD3" t="s">
         <v>44</v>
@@ -778,79 +775,79 @@
         <v>41</v>
       </c>
       <c r="C4">
-        <v>7.9</v>
+        <v>13.316</v>
       </c>
       <c r="D4">
-        <v>8.827999999999999</v>
+        <v>12.472</v>
       </c>
       <c r="E4">
-        <v>7.820194910667125</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="F4">
-        <v>9.4</v>
+        <v>11.8</v>
       </c>
       <c r="G4">
-        <v>8.347892116185454</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>7.820194910667125</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="L4">
-        <v>4.467028425282805</v>
+        <v>3.125306797245826</v>
       </c>
       <c r="M4">
         <v>5.24749619700716</v>
       </c>
       <c r="N4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
       </c>
       <c r="P4">
-        <v>8.056225323873495</v>
+        <v>12.85213593315269</v>
       </c>
       <c r="Q4">
-        <v>1.030182165010288</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R4">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.23603041320637</v>
+        <v>-0.1317477126855753</v>
       </c>
       <c r="U4">
-        <v>-0.05622532387349466</v>
+        <v>0.1478640668473066</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>8.347892116185454</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="X4">
-        <v>0.5276972055183293</v>
+        <v>0.07523380323107176</v>
       </c>
       <c r="Y4">
-        <v>0.1798050893328753</v>
+        <v>0.01611635416173129</v>
       </c>
       <c r="Z4">
-        <v>0.1181315978496199</v>
+        <v>0.02407245371794266</v>
       </c>
       <c r="AA4">
-        <v>0.04025161073862921</v>
+        <v>0.005156727069462051</v>
       </c>
       <c r="AB4">
-        <v>0.911638454139348</v>
+        <v>0.6511055827595471</v>
       </c>
       <c r="AC4">
-        <v>91.31331214761543</v>
+        <v>98.2699453837879</v>
       </c>
       <c r="AD4" t="s">
         <v>44</v>
@@ -861,85 +858,85 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5">
-        <v>1.124</v>
+        <v>172.1</v>
       </c>
       <c r="D5">
-        <v>1.364</v>
+        <v>175.156</v>
       </c>
       <c r="E5">
-        <v>1.289478939532622</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="F5">
-        <v>1.4</v>
+        <v>172.6</v>
       </c>
       <c r="G5">
-        <v>1.236806017786363</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>1.289478939532622</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="L5">
-        <v>0.9319718387197466</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M5">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N5">
-        <v>0.9</v>
+        <v>18.7</v>
       </c>
       <c r="O5" t="s">
         <v>42</v>
       </c>
       <c r="P5">
-        <v>1.053803980154308</v>
+        <v>173.8081494148196</v>
       </c>
       <c r="Q5">
-        <v>0.8172324090351291</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>-0.2356749593783138</v>
+        <v>-1.781713658384717</v>
       </c>
       <c r="U5">
-        <v>-0.05380398015430821</v>
+        <v>0.1918505851803616</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>1.236806017786363</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="X5">
-        <v>0.05267292174625871</v>
+        <v>2.014908000938448</v>
       </c>
       <c r="Y5">
-        <v>0.289478939532622</v>
+        <v>1.589863073204356</v>
       </c>
       <c r="Z5">
-        <v>0.05651771819480694</v>
+        <v>0.08157085890376452</v>
       </c>
       <c r="AA5">
-        <v>0.3106091058827276</v>
+        <v>0.06436348277948976</v>
       </c>
       <c r="AB5">
-        <v>1.035524265244163</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC5">
-        <v>86.46333766795863</v>
+        <v>92.72349650896915</v>
       </c>
       <c r="AD5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -950,82 +947,82 @@
         <v>41</v>
       </c>
       <c r="C6">
-        <v>3.096</v>
+        <v>1.412</v>
       </c>
       <c r="D6">
-        <v>4.516</v>
+        <v>1.808</v>
       </c>
       <c r="E6">
-        <v>-5.436536811828134</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="F6">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="G6">
-        <v>3.781352160542397</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="L6">
-        <v>9.933150479214353</v>
+        <v>1.746417103282563</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.717926703142854</v>
       </c>
       <c r="Q6">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.01802007627663649</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>0.2820732968571464</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>3.781352160542397</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="X6">
-        <v>3.781352160542397</v>
+        <v>0.09678024970087273</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>0.3000933731337829</v>
       </c>
       <c r="Z6">
-        <v>0.3806800439050106</v>
+        <v>0.05541645779748992</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>0.1718337346615124</v>
       </c>
       <c r="AB6">
-        <v>0.9643835416712964</v>
+        <v>0.7593117840358968</v>
       </c>
       <c r="AC6">
-        <v>78.07954833544376</v>
+        <v>90.83163983910151</v>
       </c>
       <c r="AD6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1036,82 +1033,82 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>0.656</v>
+        <v>1.164</v>
       </c>
       <c r="D7">
-        <v>0.384</v>
+        <v>1.34</v>
       </c>
       <c r="E7">
-        <v>0.4366083165842541</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="F7">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="G7">
-        <v>0.5281531798421215</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>0.4366083165842541</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="L7">
-        <v>0.7620693762924241</v>
+        <v>0.9319718387197466</v>
       </c>
       <c r="M7">
         <v>1.038416113387647</v>
       </c>
       <c r="N7">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O7" t="s">
         <v>42</v>
       </c>
       <c r="P7">
-        <v>0.5063526117264946</v>
+        <v>1.06279383028951</v>
       </c>
       <c r="Q7">
-        <v>1.159741105455516</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.06974429514224045</v>
+        <v>-0.1716086035201392</v>
       </c>
       <c r="U7">
-        <v>-0.5063526117264946</v>
+        <v>-0.06279383028951013</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>0.5281531798421215</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="X7">
-        <v>0.09154486325786737</v>
+        <v>0.01232197923368372</v>
       </c>
       <c r="Y7">
-        <v>0.4366083165842541</v>
+        <v>0.2344024338096493</v>
       </c>
       <c r="Z7">
-        <v>0.1201266788901112</v>
+        <v>0.0132214072590546</v>
       </c>
       <c r="AA7">
-        <v>0.5729246314927595</v>
+        <v>0.2515123569953024</v>
       </c>
       <c r="AB7">
-        <v>0.95258672036553</v>
+        <v>1.035524265244163</v>
       </c>
       <c r="AC7">
-        <v>75.68380671977501</v>
+        <v>90.78980016577228</v>
       </c>
       <c r="AD7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1122,82 +1119,82 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>2.568</v>
+        <v>1.128</v>
       </c>
       <c r="D8">
-        <v>3.732</v>
+        <v>1.252</v>
       </c>
       <c r="E8">
-        <v>-3.223234081728676</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="F8">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="G8">
-        <v>3.129795714698134</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="L8">
-        <v>7.059923274159115</v>
+        <v>0.8200692764238203</v>
       </c>
       <c r="M8">
         <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="s">
         <v>42</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.036948324347409</v>
       </c>
       <c r="Q8">
-        <v>1.030182165010288</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.01087699950497645</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>-0.03694832434740891</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>3.129795714698134</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="X8">
-        <v>3.129795714698134</v>
+        <v>0.1617763286133824</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>0.02607132484243246</v>
       </c>
       <c r="Z8">
-        <v>0.4433186584553801</v>
+        <v>0.1972715394470829</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.03179161272340916</v>
       </c>
       <c r="AB8">
-        <v>0.9289372729156731</v>
+        <v>0.7455175240216548</v>
       </c>
       <c r="AC8">
-        <v>74.96437929576021</v>
+        <v>86.99204005901876</v>
       </c>
       <c r="AD8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:30">
@@ -1205,85 +1202,85 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>0.216</v>
+        <v>5.304</v>
       </c>
       <c r="D9">
-        <v>0.18</v>
+        <v>4.316</v>
       </c>
       <c r="E9">
-        <v>0.01190808928740122</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="F9">
-        <v>0.2</v>
+        <v>4.4</v>
       </c>
       <c r="G9">
-        <v>0.1990790973320455</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>0.01190808928740122</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="L9">
-        <v>0.421748166646455</v>
+        <v>2.858585552684069</v>
       </c>
       <c r="M9">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N9">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="s">
         <v>42</v>
       </c>
       <c r="P9">
-        <v>0.009731676495348316</v>
+        <v>3.994458620063688</v>
       </c>
       <c r="Q9">
-        <v>0.8172324090351291</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>-0.002176412792052908</v>
+        <v>-0.04094734053139382</v>
       </c>
       <c r="U9">
-        <v>-0.009731676495348316</v>
+        <v>0.005541379936312207</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>0.1990790973320455</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="X9">
-        <v>0.1871710080446443</v>
+        <v>0.7917433812247161</v>
       </c>
       <c r="Y9">
-        <v>0.01190808928740122</v>
+        <v>0.03540596059508161</v>
       </c>
       <c r="Z9">
-        <v>0.4437980360008223</v>
+        <v>0.2769703290780675</v>
       </c>
       <c r="AA9">
-        <v>0.02823507066335061</v>
+        <v>0.01238583206363622</v>
       </c>
       <c r="AB9">
-        <v>1.054370416616137</v>
+        <v>0.6972159884595291</v>
       </c>
       <c r="AC9">
-        <v>74.20408390839145</v>
+        <v>83.16315746844765</v>
       </c>
       <c r="AD9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1294,82 +1291,82 @@
         <v>41</v>
       </c>
       <c r="C10">
-        <v>3.516</v>
+        <v>3.692</v>
       </c>
       <c r="D10">
-        <v>4.924</v>
+        <v>3.192</v>
       </c>
       <c r="E10">
-        <v>5.173756282914196</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G10">
-        <v>4.195560452143448</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>5.173756282914196</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="L10">
-        <v>2.262338789582505</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M10">
         <v>5.24749619700716</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
       </c>
       <c r="P10">
-        <v>5.329911448768128</v>
+        <v>3.440193613933819</v>
       </c>
       <c r="Q10">
-        <v>1.030182165010288</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1561551658539315</v>
+        <v>-0.03526554980344976</v>
       </c>
       <c r="U10">
-        <v>-0.3299114487681276</v>
+        <v>-0.4401936139338187</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>4.195560452143448</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="X10">
-        <v>0.9781958307707486</v>
+        <v>0.0247803470268444</v>
       </c>
       <c r="Y10">
-        <v>0.1737562829141961</v>
+        <v>0.4754591637372685</v>
       </c>
       <c r="Z10">
-        <v>0.4323825570578075</v>
+        <v>0.02791149320872625</v>
       </c>
       <c r="AA10">
-        <v>0.07680382960956141</v>
+        <v>0.5355362943587225</v>
       </c>
       <c r="AB10">
-        <v>0.452467757916501</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC10">
-        <v>73.49667620805681</v>
+        <v>81.41748166151876</v>
       </c>
       <c r="AD10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1377,85 +1374,85 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11">
-        <v>0.652</v>
+        <v>3.184</v>
       </c>
       <c r="D11">
-        <v>0.612</v>
+        <v>4.004</v>
       </c>
       <c r="E11">
-        <v>0.2977289224579263</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="G11">
-        <v>0.633198997035606</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.2977289224579263</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="L11">
-        <v>1.005444112310955</v>
+        <v>7.059923274159115</v>
       </c>
       <c r="M11">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N11">
-        <v>0.9</v>
+        <v>7.6</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
       </c>
       <c r="P11">
-        <v>0.2433137245397242</v>
+        <v>1.566812662552681</v>
       </c>
       <c r="Q11">
-        <v>0.8172324090351291</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
       </c>
       <c r="T11">
-        <v>-0.05441519791820207</v>
+        <v>0.01643497574066832</v>
       </c>
       <c r="U11">
-        <v>-0.2433137245397242</v>
+        <v>0.433187337447319</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.633198997035606</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="X11">
-        <v>0.3354700745776797</v>
+        <v>2.029389053782892</v>
       </c>
       <c r="Y11">
-        <v>0.2977289224579263</v>
+        <v>0.4496223131879873</v>
       </c>
       <c r="Z11">
-        <v>0.3336536267606375</v>
+        <v>0.2874519984106493</v>
       </c>
       <c r="AA11">
-        <v>0.296116829182692</v>
+        <v>0.06368657218042365</v>
       </c>
       <c r="AB11">
-        <v>1.117160124789949</v>
+        <v>0.9289372729156731</v>
       </c>
       <c r="AC11">
-        <v>72.57746240041317</v>
+        <v>81.12864354622022</v>
       </c>
       <c r="AD11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
